--- a/artfynd/A 584-2025 artfynd.xlsx
+++ b/artfynd/A 584-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123397971</v>
+        <v>123396252</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -723,17 +723,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ljungabolet, Sk</t>
+          <t>Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376584</v>
+        <v>376551</v>
       </c>
       <c r="R2" t="n">
-        <v>6243510</v>
+        <v>6243657</v>
       </c>
       <c r="S2" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123398476</v>
+        <v>123397971</v>
       </c>
       <c r="B3" t="n">
-        <v>57629</v>
+        <v>57851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,25 +832,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästhagen, Hästhagen, Sk</t>
+          <t>Ljungabolet, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376573</v>
+        <v>376584</v>
       </c>
       <c r="R3" t="n">
-        <v>6243599</v>
+        <v>6243510</v>
       </c>
       <c r="S3" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123396252</v>
+        <v>123398476</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,16 +939,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,32 +956,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästhagen, Sk</t>
+          <t>Hästhagen, Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376551</v>
+        <v>376573</v>
       </c>
       <c r="R4" t="n">
-        <v>6243657</v>
+        <v>6243599</v>
       </c>
       <c r="S4" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 584-2025 artfynd.xlsx
+++ b/artfynd/A 584-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123396252</v>
+        <v>123397971</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>57851</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -723,17 +723,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hästhagen, Sk</t>
+          <t>Ljungabolet, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376551</v>
+        <v>376584</v>
       </c>
       <c r="R2" t="n">
-        <v>6243657</v>
+        <v>6243510</v>
       </c>
       <c r="S2" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123397971</v>
+        <v>123398476</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,32 +832,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ljungabolet, Sk</t>
+          <t>Hästhagen, Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376584</v>
+        <v>376573</v>
       </c>
       <c r="R3" t="n">
-        <v>6243510</v>
+        <v>6243599</v>
       </c>
       <c r="S3" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123398476</v>
+        <v>123396252</v>
       </c>
       <c r="B4" t="n">
-        <v>57632</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,16 +932,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -956,25 +949,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästhagen, Hästhagen, Sk</t>
+          <t>Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376573</v>
+        <v>376551</v>
       </c>
       <c r="R4" t="n">
-        <v>6243599</v>
+        <v>6243657</v>
       </c>
       <c r="S4" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 584-2025 artfynd.xlsx
+++ b/artfynd/A 584-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123397971</v>
+        <v>123398476</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,32 +708,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ljungabolet, Sk</t>
+          <t>Hästhagen, Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376584</v>
+        <v>376573</v>
       </c>
       <c r="R2" t="n">
-        <v>6243510</v>
+        <v>6243599</v>
       </c>
       <c r="S2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123398476</v>
+        <v>123396252</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,25 +825,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästhagen, Hästhagen, Sk</t>
+          <t>Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376573</v>
+        <v>376551</v>
       </c>
       <c r="R3" t="n">
-        <v>6243599</v>
+        <v>6243657</v>
       </c>
       <c r="S3" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123396252</v>
+        <v>123397971</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>57851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,20 +928,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -964,17 +964,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästhagen, Sk</t>
+          <t>Ljungabolet, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376551</v>
+        <v>376584</v>
       </c>
       <c r="R4" t="n">
-        <v>6243657</v>
+        <v>6243510</v>
       </c>
       <c r="S4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 584-2025 artfynd.xlsx
+++ b/artfynd/A 584-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123398476</v>
+        <v>123397971</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
+        <v>57851</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,25 +708,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hästhagen, Hästhagen, Sk</t>
+          <t>Ljungabolet, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376573</v>
+        <v>376584</v>
       </c>
       <c r="R2" t="n">
-        <v>6243599</v>
+        <v>6243510</v>
       </c>
       <c r="S2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123396252</v>
+        <v>123398476</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,16 +815,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,32 +832,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästhagen, Sk</t>
+          <t>Hästhagen, Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376551</v>
+        <v>376573</v>
       </c>
       <c r="R3" t="n">
-        <v>6243657</v>
+        <v>6243599</v>
       </c>
       <c r="S3" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123397971</v>
+        <v>123396252</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,20 +928,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -964,17 +964,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ljungabolet, Sk</t>
+          <t>Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376584</v>
+        <v>376551</v>
       </c>
       <c r="R4" t="n">
-        <v>6243510</v>
+        <v>6243657</v>
       </c>
       <c r="S4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 584-2025 artfynd.xlsx
+++ b/artfynd/A 584-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123397971</v>
+        <v>123396252</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>57503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -723,17 +723,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ljungabolet, Sk</t>
+          <t>Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376584</v>
+        <v>376551</v>
       </c>
       <c r="R2" t="n">
-        <v>6243510</v>
+        <v>6243657</v>
       </c>
       <c r="S2" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,7 +802,7 @@
         <v>123398476</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
+        <v>57638</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123396252</v>
+        <v>123397971</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>57857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,20 +928,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -964,17 +964,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästhagen, Sk</t>
+          <t>Ljungabolet, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376551</v>
+        <v>376584</v>
       </c>
       <c r="R4" t="n">
-        <v>6243657</v>
+        <v>6243510</v>
       </c>
       <c r="S4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 584-2025 artfynd.xlsx
+++ b/artfynd/A 584-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123396252</v>
+        <v>123398476</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
+        <v>57641</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,32 +708,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hästhagen, Sk</t>
+          <t>Hästhagen, Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376551</v>
+        <v>376573</v>
       </c>
       <c r="R2" t="n">
-        <v>6243657</v>
+        <v>6243599</v>
       </c>
       <c r="S2" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123398476</v>
+        <v>123396252</v>
       </c>
       <c r="B3" t="n">
-        <v>57638</v>
+        <v>57506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,25 +825,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästhagen, Hästhagen, Sk</t>
+          <t>Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376573</v>
+        <v>376551</v>
       </c>
       <c r="R3" t="n">
-        <v>6243599</v>
+        <v>6243657</v>
       </c>
       <c r="S3" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
         <v>123397971</v>
       </c>
       <c r="B4" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 584-2025 artfynd.xlsx
+++ b/artfynd/A 584-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123398476</v>
       </c>
       <c r="B2" t="n">
-        <v>57641</v>
+        <v>57642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>123396252</v>
       </c>
       <c r="B3" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>123397971</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 584-2025 artfynd.xlsx
+++ b/artfynd/A 584-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123398476</v>
+        <v>123396252</v>
       </c>
       <c r="B2" t="n">
-        <v>57642</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,25 +708,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hästhagen, Hästhagen, Sk</t>
+          <t>Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376573</v>
+        <v>376551</v>
       </c>
       <c r="R2" t="n">
-        <v>6243599</v>
+        <v>6243657</v>
       </c>
       <c r="S2" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123396252</v>
+        <v>123398476</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>57642</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,16 +815,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,32 +832,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästhagen, Sk</t>
+          <t>Hästhagen, Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376551</v>
+        <v>376573</v>
       </c>
       <c r="R3" t="n">
-        <v>6243657</v>
+        <v>6243599</v>
       </c>
       <c r="S3" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 584-2025 artfynd.xlsx
+++ b/artfynd/A 584-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123396252</v>
+        <v>123397971</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -723,17 +723,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hästhagen, Sk</t>
+          <t>Ljungabolet, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376551</v>
+        <v>376584</v>
       </c>
       <c r="R2" t="n">
-        <v>6243657</v>
+        <v>6243510</v>
       </c>
       <c r="S2" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123398476</v>
+        <v>123396252</v>
       </c>
       <c r="B3" t="n">
-        <v>57642</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,25 +832,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästhagen, Hästhagen, Sk</t>
+          <t>Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376573</v>
+        <v>376551</v>
       </c>
       <c r="R3" t="n">
-        <v>6243599</v>
+        <v>6243657</v>
       </c>
       <c r="S3" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123397971</v>
+        <v>123398476</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>57642</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,20 +935,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,32 +956,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ljungabolet, Sk</t>
+          <t>Hästhagen, Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376584</v>
+        <v>376573</v>
       </c>
       <c r="R4" t="n">
-        <v>6243510</v>
+        <v>6243599</v>
       </c>
       <c r="S4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 584-2025 artfynd.xlsx
+++ b/artfynd/A 584-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123397971</v>
+        <v>123398476</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>57642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,32 +708,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ljungabolet, Sk</t>
+          <t>Hästhagen, Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376584</v>
+        <v>376573</v>
       </c>
       <c r="R2" t="n">
-        <v>6243510</v>
+        <v>6243599</v>
       </c>
       <c r="S2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123396252</v>
+        <v>123397971</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +804,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -847,17 +840,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästhagen, Sk</t>
+          <t>Ljungabolet, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376551</v>
+        <v>376584</v>
       </c>
       <c r="R3" t="n">
-        <v>6243657</v>
+        <v>6243510</v>
       </c>
       <c r="S3" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123398476</v>
+        <v>123396252</v>
       </c>
       <c r="B4" t="n">
-        <v>57642</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,16 +932,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -956,25 +949,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästhagen, Hästhagen, Sk</t>
+          <t>Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376573</v>
+        <v>376551</v>
       </c>
       <c r="R4" t="n">
-        <v>6243599</v>
+        <v>6243657</v>
       </c>
       <c r="S4" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 584-2025 artfynd.xlsx
+++ b/artfynd/A 584-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123397971</v>
+        <v>123396252</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -723,17 +718,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ljungabolet, Sk</t>
+          <t>Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376584</v>
+        <v>376551</v>
       </c>
       <c r="R2" t="n">
-        <v>6243510</v>
+        <v>6243657</v>
       </c>
       <c r="S2" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,32 +794,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123398476</v>
+        <v>123397971</v>
       </c>
       <c r="B3" t="n">
-        <v>57664</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,25 +822,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästhagen, Hästhagen, Sk</t>
+          <t>Ljungabolet, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376573</v>
+        <v>376584</v>
       </c>
       <c r="R3" t="n">
-        <v>6243599</v>
+        <v>6243510</v>
       </c>
       <c r="S3" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,15 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123396252</v>
+        <v>123398476</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,16 +924,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,32 +941,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästhagen, Sk</t>
+          <t>Hästhagen, Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376551</v>
+        <v>376573</v>
       </c>
       <c r="R4" t="n">
-        <v>6243657</v>
+        <v>6243599</v>
       </c>
       <c r="S4" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,6 +1022,123 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123394364</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ljungabolet, Västersjön, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>376539</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6243807</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 584-2025 artfynd.xlsx
+++ b/artfynd/A 584-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123396252</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123397971</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123398476</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,8 +1159,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123394364</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>